--- a/Risk_Register/GRC_Intelligence_Risk_Register_2026-06-15.xlsx
+++ b/Risk_Register/GRC_Intelligence_Risk_Register_2026-06-15.xlsx
@@ -904,7 +904,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:X20"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="41" min="1" max="1"/>
     <col width="14" customWidth="1" style="41" min="2" max="2"/>
@@ -931,14 +931,14 @@
     <row r="1" ht="39.75" customHeight="1" s="42">
       <c r="A1" s="43" t="inlineStr">
         <is>
-          <t>BLAISE KINGKO — GRC INTELLIGENCE &amp; RISK REGISTER</t>
+          <t>BLAISE KINGKO — GRC INTELLIGENCE &amp; RISK REGISTER   [ ARCHIVED SNAPSHOT: v3 — 2026-06-15 ]</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" s="42">
       <c r="A2" s="44" t="inlineStr">
         <is>
-          <t>Sources: CISA KEV | US-CERT | NIST NVD | AWS/Azure Bulletins | AI Governance Updates   |   Frameworks: NIST CSF 2.0 | ISO 27001 | NIST 800-53 | CIS Controls | NIST AI RMF | ISO 42001 | EU AI Act   |   Last Updated: 2026-05-29</t>
+          <t>ARCHIVED SNAPSHOT — v3 — 2026-06-15 — NOT LIVE. This is a frozen point-in-time copy; do not edit. For the current/live register, use GRC_Intelligence_Risk_Register.xlsx in this folder.   |   Sources: CISA KEV | US-CERT | NIST NVD | AWS/Azure Bulletins | AI Governance Updates   |   Frameworks: NIST CSF 2.0 | ISO 27001 | NIST 800-53 | CIS Controls | NIST AI RMF | ISO 42001 | EU AI Act   |   Last Updated: 2026-05-29</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="39.75" customHeight="1" s="42">
       <c r="A5" s="52" t="inlineStr">
         <is>
@@ -9917,7 +9916,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="41" min="1" max="1"/>
     <col width="28" customWidth="1" style="41" min="2" max="2"/>
@@ -10263,7 +10262,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="20" customWidth="1" style="41" min="1" max="1"/>
     <col width="14" customWidth="1" style="41" min="2" max="6"/>
@@ -10544,7 +10543,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="41" min="1" max="1"/>
     <col width="24" customWidth="1" style="41" min="2" max="2"/>
